--- a/outputs/worship_planning_2026-01-04_2026-06-28.xlsx
+++ b/outputs/worship_planning_2026-01-04_2026-06-28.xlsx
@@ -486,33 +486,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Gabriel Romero</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sofía Medina</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tomás Ortega</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Samuel Molina</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>Samuel Ortega</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Thomas Walker</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Lucia Mendoza</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
+          <t>Lucía Rojas</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
     </row>
@@ -530,28 +534,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Isabella Palacios</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Mateo Cabrera</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>Valentina Salazar</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Valentina Fuentes</t>
+          <t>Mateo Santos</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -574,35 +582,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Samuel Ortega</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Daniel Herrera</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mariana Campos</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Samuel Molina</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Mariana Campos</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Gabriel Romero</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Lucy Bennett</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Samuel Molina</t>
-        </is>
-      </c>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -618,7 +622,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -633,13 +637,13 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Matthew Brooks</t>
+          <t>Mateo Cabrera</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Nicholas Reed</t>
+          <t>Nicolás Mendoza</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -662,7 +666,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Thomas Walker</t>
+          <t>Samuel Molina</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -672,22 +676,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mariana Campos</t>
+          <t>Tomás Ortega</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lucia Mendoza</t>
+          <t>Lucía Mendoza</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Samuel Ortega</t>
+          <t>Gabriel Romero</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
+          <t>Valentina Fuentes</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -710,32 +714,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nicolás Mendoza</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Mateo Cabrera</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>Isabella Palacios</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Valentina Salazar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Nicholas Reed</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -758,17 +762,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Gabriel Romero</t>
+          <t>Tomás Ortega</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomas Walker</t>
+          <t>Mariana Campos</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -783,12 +787,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Lucy Bennett</t>
+          <t>Lucía Rojas</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
     </row>
@@ -806,33 +810,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Mateo Cabrera</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Bruno Vega</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Nicholas Reed</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
+          <t>Mateo Santos</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
     </row>
@@ -850,14 +850,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Valentina Fuentes</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Mariana Campos</t>
@@ -865,13 +865,13 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lucia Mendoza</t>
+          <t>Lucía Mendoza</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Valentina Fuentes</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -890,25 +890,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Matthew Brooks</t>
+          <t>Valentina Salazar</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thomas Walker</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Valentina Salazar</t>
-        </is>
-      </c>
+          <t>Tomás Ortega</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Mateo Cabrera</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Isabella Palacios</t>
@@ -916,7 +916,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lucy Bennett</t>
+          <t>Lucía Rojas</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -952,19 +952,15 @@
           <t>Samuel Molina</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Gabriel Romero</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
+          <t>Mateo Santos</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
     </row>
@@ -982,12 +978,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nicholas Reed</t>
+          <t>Nicolás Mendoza</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -997,7 +993,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Matthew Brooks</t>
+          <t>Mateo Cabrera</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1008,7 +1004,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1022,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Samuel Molina</t>
+          <t>Valentina Fuentes</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1041,20 +1037,16 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lucia Mendoza</t>
+          <t>Lucía Mendoza</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Valentina Fuentes</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
+          <t>Sofía Medina</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1070,33 +1062,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>Gabriel Romero</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tomás Ortega</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Samuel Molina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>Samuel Ortega</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Thomas Walker</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
+          <t>Mateo Santos</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
     </row>
@@ -1114,29 +1110,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Isabella Palacios</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Mateo Cabrera</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>Valentina Salazar</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Isabella Palacios</t>
+          <t>Nicolás Mendoza</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
     </row>
@@ -1154,37 +1158,33 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Samuel Ortega</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mariana Campos</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>Samuel Molina</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Mariana Campos</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Gabriel Romero</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Lucy Bennett</t>
+          <t>Lucía Rojas</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Samuel Molina</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1215,16 +1215,20 @@
           <t>Bruno Vega</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Mateo Cabrera</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Nicholas Reed</t>
+          <t>Valentina Fuentes</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
     </row>
@@ -1242,22 +1246,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Thomas Walker</t>
+          <t>Samuel Molina</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mariana Campos</t>
+          <t>Tomás Ortega</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lucia Mendoza</t>
+          <t>Lucía Mendoza</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1267,12 +1271,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
+          <t>Mateo Santos</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
     </row>
@@ -1290,37 +1294,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nicolás Mendoza</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Mateo Cabrera</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>Isabella Palacios</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Valentina Salazar</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Nicholas Reed</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
     </row>
@@ -1338,37 +1342,37 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>Tomás Ortega</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mariana Campos</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Samuel Molina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>Gabriel Romero</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Thomas Walker</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Samuel Molina</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Samuel Ortega</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Lucy Bennett</t>
+          <t>Lucía Rojas</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
     </row>
@@ -1386,33 +1390,29 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>Mateo Cabrera</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sofía Medina</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Bruno Vega</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Nicholas Reed</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
+          <t>Valentina Fuentes</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Valentina Fuentes</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mariana Campos</t>
+          <t>Tomás Ortega</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lucia Mendoza</t>
+          <t>Lucía Mendoza</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1455,10 +1455,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>Mateo Santos</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1474,25 +1478,21 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Matthew Brooks</t>
+          <t>Valentina Salazar</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Mateo Cabrera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Thomas Walker</t>
+          <t>Bruno Vega</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Valentina Salazar</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Isabella Palacios</t>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Mateo Cabrera</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Lucy Bennett</t>
+          <t>Lucía Rojas</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1538,19 +1538,15 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Gabriel Romero</t>
+          <t>Samuel Ortega</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
+          <t>Sofía Medina</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1566,7 +1562,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Nicholas Reed</t>
+          <t>Nicolás Mendoza</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1576,18 +1572,18 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bruno Vega</t>
+          <t>Tomás Ortega</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Matthew Brooks</t>
+          <t>Mateo Cabrera</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Isabella Palacios</t>
+          <t>Mateo Santos</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1610,7 +1606,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Samuel Molina</t>
+          <t>Valentina Fuentes</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1625,20 +1621,16 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lucia Mendoza</t>
+          <t>Lucía Mendoza</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Valentina Fuentes</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
           <t>Daniel Herrera</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/worship_planning_2026-01-04_2026-06-28.xlsx
+++ b/outputs/worship_planning_2026-01-04_2026-06-28.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sofía Medina</t>
+          <t>Sophia Carter</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tomás Ortega</t>
+          <t>Thomas Walker</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,12 +511,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Lucía Rojas</t>
+          <t>Lucy Bennett</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sofía Medina</t>
+          <t>Sophia Carter</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mateo Cabrera</t>
+          <t>Matthew Brooks</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -559,12 +559,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Mateo Santos</t>
+          <t>Matthew Turner</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -603,7 +603,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -622,12 +622,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sofía Medina</t>
+          <t>Sophia Carter</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -637,18 +637,18 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mateo Cabrera</t>
+          <t>Matthew Brooks</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Nicolás Mendoza</t>
+          <t>Nicholas Reed</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
     </row>
@@ -666,27 +666,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Samuel Molina</t>
+          <t>Thomas Walker</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tomás Ortega</t>
+          <t>Mariana Campos</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lucía Mendoza</t>
+          <t>Lucia Mendoza</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Gabriel Romero</t>
+          <t>Samuel Ortega</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
     </row>
@@ -719,17 +719,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nicolás Mendoza</t>
+          <t>Nicholas Reed</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Mateo Cabrera</t>
+          <t>Matthew Brooks</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -739,12 +739,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Isabella Palacios</t>
+          <t>Matthew Turner</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tomás Ortega</t>
+          <t>Lucy Bennett</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sofía Medina</t>
+          <t>Sophia Carter</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -782,19 +782,15 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Samuel Ortega</t>
+          <t>Gabriel Romero</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Lucía Rojas</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Sofía Medina</t>
-        </is>
-      </c>
+          <t>Sophia Carter</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -810,7 +806,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mateo Cabrera</t>
+          <t>Matthew Brooks</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -820,14 +816,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bruno Vega</t>
+          <t>Thomas Walker</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Mateo Santos</t>
+          <t>Isabella Palacios</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -865,16 +861,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lucía Mendoza</t>
+          <t>Lucia Mendoza</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Matthew Turner</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>Valentina Fuentes</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -895,28 +895,28 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sofía Medina</t>
+          <t>Sophia Carter</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tomás Ortega</t>
+          <t>Bruno Vega</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mateo Cabrera</t>
+          <t>Matthew Brooks</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Isabella Palacios</t>
+          <t>Nicholas Reed</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sofía Medina</t>
+          <t>Sophia Carter</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lucía Rojas</t>
+          <t>Samuel Molina</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -944,18 +944,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mariana Campos</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Samuel Molina</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Thomas Walker</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Samuel Ortega</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Mateo Santos</t>
+          <t>Lucy Bennett</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nicolás Mendoza</t>
+          <t>Nicholas Reed</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Mateo Cabrera</t>
+          <t>Matthew Brooks</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sofía Medina</t>
+          <t>Sophia Carter</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1037,16 +1037,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lucía Mendoza</t>
+          <t>Lucia Mendoza</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Sofía Medina</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>Matthew Turner</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sophia Carter</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1072,7 +1076,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tomás Ortega</t>
+          <t>Thomas Walker</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1087,7 +1091,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Mateo Santos</t>
+          <t>Lucy Bennett</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1125,7 +1129,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Mateo Cabrera</t>
+          <t>Matthew Brooks</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1135,7 +1139,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nicolás Mendoza</t>
+          <t>Nicholas Reed</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1179,7 +1183,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Lucía Rojas</t>
+          <t>Matthew Turner</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1202,7 +1206,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sofía Medina</t>
+          <t>Sophia Carter</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1217,7 +1221,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Mateo Cabrera</t>
+          <t>Matthew Brooks</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1246,7 +1250,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Samuel Molina</t>
+          <t>Thomas Walker</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1256,12 +1260,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tomás Ortega</t>
+          <t>Mariana Campos</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lucía Mendoza</t>
+          <t>Lucia Mendoza</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1271,14 +1275,10 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Mateo Santos</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nicolás Mendoza</t>
+          <t>Nicholas Reed</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Mateo Cabrera</t>
+          <t>Matthew Brooks</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tomás Ortega</t>
+          <t>Lucy Bennett</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Lucía Rojas</t>
+          <t>Matthew Turner</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1390,12 +1390,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mateo Cabrera</t>
+          <t>Matthew Brooks</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sofía Medina</t>
+          <t>Sophia Carter</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sofía Medina</t>
+          <t>Sophia Carter</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tomás Ortega</t>
+          <t>Thomas Walker</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lucía Mendoza</t>
+          <t>Lucia Mendoza</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1455,14 +1455,10 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Mateo Santos</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1483,7 +1479,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mateo Cabrera</t>
+          <t>Matthew Brooks</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1500,7 +1496,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Mateo Cabrera</t>
+          <t>Matthew Brooks</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1514,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Lucía Rojas</t>
+          <t>Samuel Molina</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sofía Medina</t>
+          <t>Sophia Carter</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1531,11 +1527,7 @@
           <t>Mariana Campos</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Samuel Molina</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Samuel Ortega</t>
@@ -1543,10 +1535,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Sofía Medina</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>Matthew Turner</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sophia Carter</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1562,33 +1558,33 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Nicolás Mendoza</t>
+          <t>Nicholas Reed</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tomás Ortega</t>
+          <t>Thomas Walker</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Mateo Cabrera</t>
+          <t>Matthew Brooks</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Mateo Santos</t>
+          <t>Isabella Palacios</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1607,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1621,16 +1617,20 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lucía Mendoza</t>
+          <t>Lucia Mendoza</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>Lucy Bennett</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/worship_planning_2026-01-04_2026-06-28.xlsx
+++ b/outputs/worship_planning_2026-01-04_2026-06-28.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,62 +433,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Rehearsal Date (Saturday)</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Service Date (Sunday)</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Tentative Rehearsal Time</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Guitarist</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Drummer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Bassist</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Keyboardist</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Vocalist_1</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Vocalist_2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>46026</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,82 +498,78 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Samuel Molina</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Thomas Walker</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Matthew Brooks</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>Gabriel Romero</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Lucy Bennett</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46032</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Saturday morning</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Sophia Carter</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Thomas Walker</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Samuel Molina</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Samuel Ortega</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Lucy Bennett</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46032</v>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Saturday morning</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Isabella Palacios</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Valentina Salazar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Matthew Turner</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Daniel Herrera</t>
@@ -569,10 +577,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46039</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>46040</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -603,26 +611,30 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Matthew Turner</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46046</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>46047</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Saturday morning</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Lucy Bennett</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -632,7 +644,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bruno Vega</t>
+          <t>Lucia Mendoza</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -643,244 +655,244 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Valentina Fuentes</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Saturday morning</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>Nicholas Reed</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sophia Carter</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Isabella Palacios</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sophia Carter</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46060</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>46061</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Saturday afternoon</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Thomas Walker</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Mariana Campos</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Samuel Molina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Samuel Ortega</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Matthew Turner</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46067</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>46068</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Saturday morning</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Matthew Brooks</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Nicholas Reed</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Matthew Brooks</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>46075</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Saturday afternoon</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Gabriel Romero</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mariana Campos</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Lucia Mendoza</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Samuel Ortega</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Valentina Fuentes</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46060</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>46061</v>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Lucy Bennett</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Saturday morning</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sophia Carter</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Bruno Vega</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Nicholas Reed</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Valentina Salazar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Matthew Turner</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46067</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>46068</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Saturday afternoon</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Lucy Bennett</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Mariana Campos</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Samuel Molina</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Gabriel Romero</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46074</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>46075</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Saturday morning</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Thomas Walker</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Isabella Palacios</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>46082</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Saturday afternoon</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Valentina Fuentes</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Mariana Campos</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Lucia Mendoza</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
+          <t>Valentina Fuentes</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Valentina Fuentes</t>
+          <t>Sophia Carter</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>46089</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -890,41 +902,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Valentina Salazar</t>
+          <t>Isabella Palacios</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
+          <t>Thomas Walker</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Nicholas Reed</t>
+          <t>Matthew Turner</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>46096</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -934,72 +942,68 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>Matthew Brooks</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mariana Campos</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>Samuel Molina</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Lucy Bennett</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Saturday morning</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Thomas Walker</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Samuel Ortega</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Lucy Bennett</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>46102</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>46103</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Saturday morning</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Nicholas Reed</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Isabella Palacios</t>
+          <t>Nicholas Reed</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1009,10 +1013,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>46109</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>46110</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -1027,7 +1031,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1048,126 +1052,122 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Saturday afternoon</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Samuel Molina</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Thomas Walker</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Matthew Brooks</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Gabriel Romero</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Lucy Bennett</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Saturday morning</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>Sophia Carter</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46116</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>46117</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Isabella Palacios</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>46131</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Saturday afternoon</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Gabriel Romero</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Thomas Walker</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Samuel Molina</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Samuel Ortega</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Lucy Bennett</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46123</v>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Saturday morning</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Isabella Palacios</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Valentina Salazar</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Nicholas Reed</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>46131</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Saturday afternoon</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Samuel Ortega</t>
-        </is>
-      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1188,35 +1188,35 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saturday morning</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Lucy Bennett</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bruno Vega</t>
+          <t>Lucia Mendoza</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1232,239 +1232,235 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>46145</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Saturday morning</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Nicholas Reed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sophia Carter</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Isabella Palacios</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sophia Carter</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Saturday afternoon</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Thomas Walker</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Mariana Campos</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Samuel Molina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Samuel Ortega</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Matthew Turner</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Saturday morning</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Matthew Brooks</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Nicholas Reed</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Matthew Brooks</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Saturday afternoon</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Gabriel Romero</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sophia Carter</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mariana Campos</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>Lucia Mendoza</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Samuel Ortega</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>46151</v>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>46152</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Saturday morning</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Nicholas Reed</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Valentina Salazar</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Isabella Palacios</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46158</v>
-      </c>
-      <c r="B21" s="1" t="n">
-        <v>46159</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Saturday afternoon</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Lucy Bennett</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Mariana Campos</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Samuel Molina</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Gabriel Romero</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Matthew Turner</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Saturday morning</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
+          <t>Lucy Bennett</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sophia Carter</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Saturday morning</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Thomas Walker</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Matthew Brooks</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>Valentina Fuentes</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46172</v>
-      </c>
-      <c r="B23" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Saturday afternoon</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Thomas Walker</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Lucia Mendoza</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Samuel Ortega</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46179</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>46180</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1474,12 +1470,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Valentina Salazar</t>
+          <t>Isabella Palacios</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Matthew Brooks</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1491,64 +1487,68 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Isabella Palacios</t>
+          <t>Matthew Turner</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Saturday afternoon</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>Matthew Brooks</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>46186</v>
-      </c>
-      <c r="B25" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Saturday afternoon</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sophia Carter</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mariana Campos</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>Samuel Molina</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Samuel Ortega</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Lucy Bennett</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>Sophia Carter</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Mariana Campos</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Samuel Ortega</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Matthew Turner</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46193</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>46194</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Nicholas Reed</t>
+          <t>Bruno Vega</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1571,28 +1571,24 @@
           <t>Thomas Walker</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Isabella Palacios</t>
+          <t>Nicholas Reed</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46200</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>46201</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -1607,7 +1603,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1623,12 +1619,12 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Lucy Bennett</t>
+          <t>Matthew Turner</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
     </row>

--- a/outputs/worship_planning_2026-01-04_2026-06-28.xlsx
+++ b/outputs/worship_planning_2026-01-04_2026-06-28.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,62 +421,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Rehearsal Date (Saturday)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Service Date (Sunday)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Tentative Rehearsal Time</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Guitarist</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Drummer</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Bassist</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Keyboardist</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Vocalist_1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Vocalist_2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>46025</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="1" t="n">
         <v>46026</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -498,12 +486,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Samuel Molina</t>
+          <t>Gabriel Romero</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -513,74 +501,74 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Lucia Mendoza</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Samuel Ortega</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Matthew Turner</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46032</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Saturday morning</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Isabella Palacios</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Matthew Brooks</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Gabriel Romero</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Lucy Bennett</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>46032</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>46033</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Saturday morning</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Valentina Salazar</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Isabella Palacios</t>
+          <t>Valentina Fuentes</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="1" t="n">
         <v>46040</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -595,7 +583,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -611,328 +599,316 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Lucy Bennett</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46046</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46047</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Saturday morning</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sophia Carter</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nicholas Reed</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Matthew Turner</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>46046</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>46047</v>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sophia Carter</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Saturday afternoon</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Thomas Walker</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lucia Mendoza</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Samuel Ortega</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46060</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46061</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Saturday morning</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Nicholas Reed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Matthew Brooks</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Isabella Palacios</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Matthew Brooks</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46067</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46068</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Saturday afternoon</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Samuel Molina</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sophia Carter</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mariana Campos</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Gabriel Romero</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Lucy Bennett</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sophia Carter</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Saturday morning</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Matthew Brooks</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Matthew Turner</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Saturday afternoon</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Valentina Fuentes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mariana Campos</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Lucia Mendoza</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Valentina Fuentes</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>46054</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Saturday morning</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Nicholas Reed</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Valentina Salazar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Isabella Palacios</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>46060</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>46061</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Saturday afternoon</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Thomas Walker</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Mariana Campos</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Samuel Molina</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Samuel Ortega</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Matthew Turner</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>46067</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>46068</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Saturday morning</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Nicholas Reed</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>46074</v>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>46075</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Saturday afternoon</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Gabriel Romero</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Mariana Campos</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Lucia Mendoza</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Samuel Ortega</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Lucy Bennett</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>46082</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Saturday morning</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Valentina Salazar</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Valentina Fuentes</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Saturday morning</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Sophia Carter</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>46088</v>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>46089</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Saturday morning</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Isabella Palacios</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>Thomas Walker</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Matthew Brooks</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
+          <t>Isabella Palacios</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Sophia Carter</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>46095</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="1" t="n">
         <v>46096</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -942,7 +918,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Matthew Brooks</t>
+          <t>Lucy Bennett</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -963,7 +939,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Lucy Bennett</t>
+          <t>Matthew Turner</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -973,10 +949,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="1" t="n">
         <v>46103</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -986,20 +962,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Thomas Walker</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Bruno Vega</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Thomas Walker</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Matthew Brooks</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
@@ -1013,10 +993,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>46109</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -1026,7 +1006,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Valentina Fuentes</t>
+          <t>Sophia Carter</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1047,91 +1027,95 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
+          <t>Valentina Fuentes</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46117</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Saturday afternoon</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Gabriel Romero</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Thomas Walker</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Samuel Molina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Samuel Ortega</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>Matthew Turner</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>46116</v>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>46117</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Saturday afternoon</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Samuel Molina</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Thomas Walker</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46123</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46124</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Saturday morning</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Isabella Palacios</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>Matthew Brooks</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Gabriel Romero</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Lucy Bennett</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>46123</v>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Saturday morning</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Valentina Salazar</t>
@@ -1139,7 +1123,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Isabella Palacios</t>
+          <t>Nicholas Reed</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1149,10 +1133,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>46130</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" s="1" t="n">
         <v>46131</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -1183,7 +1167,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
+          <t>Lucy Bennett</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1193,37 +1177,33 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>46137</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="1" t="n">
         <v>46138</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saturday afternoon</t>
+          <t>Saturday morning</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Lucy Bennett</t>
+          <t>Bruno Vega</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Sophia Carter</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lucia Mendoza</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
+          <t>Nicholas Reed</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
@@ -1232,178 +1212,178 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Sophia Carter</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>46144</v>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" s="1" t="n">
         <v>46145</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Saturday afternoon</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Thomas Walker</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lucia Mendoza</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Samuel Ortega</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Matthew Turner</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Saturday morning</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Nicholas Reed</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Matthew Brooks</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Isabella Palacios</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>46159</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Saturday afternoon</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Samuel Molina</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mariana Campos</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Gabriel Romero</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Lucy Bennett</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Saturday morning</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Matthew Brooks</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>Sophia Carter</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Bruno Vega</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Valentina Salazar</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Isabella Palacios</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>46151</v>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>46152</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Saturday afternoon</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Thomas Walker</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Mariana Campos</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Samuel Molina</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Samuel Ortega</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Matthew Turner</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>46158</v>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>46159</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Saturday morning</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Nicholas Reed</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>46166</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Saturday afternoon</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Gabriel Romero</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Mariana Campos</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Lucia Mendoza</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Lucy Bennett</t>
+          <t>Matthew Turner</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1413,165 +1393,169 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46172</v>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>Saturday afternoon</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Valentina Fuentes</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Thomas Walker</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lucia Mendoza</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Samuel Ortega</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>46180</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Saturday morning</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Valentina Salazar</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Thomas Walker</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>Matthew Brooks</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Valentina Fuentes</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>46179</v>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>46180</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Saturday morning</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Isabella Palacios</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
+          <t>Isabella Palacios</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Saturday afternoon</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Lucy Bennett</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mariana Campos</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Samuel Molina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>Matthew Turner</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>46186</v>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Saturday afternoon</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Saturday morning</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Thomas Walker</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>Matthew Brooks</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Mariana Campos</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Samuel Molina</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Samuel Ortega</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Lucy Bennett</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>46193</v>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Saturday morning</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Thomas Walker</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
@@ -1585,10 +1569,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46200</v>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B27" s="1" t="n">
         <v>46201</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -1598,7 +1582,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Valentina Fuentes</t>
+          <t>Sophia Carter</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1619,7 +1603,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
+          <t>Valentina Fuentes</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">

--- a/outputs/worship_planning_2026-01-04_2026-06-28.xlsx
+++ b/outputs/worship_planning_2026-01-04_2026-06-28.xlsx
@@ -486,37 +486,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Gabriel Romero</t>
+          <t>Samuel Ortega</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomas Walker</t>
+          <t>Tomás Ortega</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lucia Mendoza</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Samuel Ortega</t>
-        </is>
-      </c>
+          <t>Samuel Molina</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
+          <t>Mateo Santos</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
     </row>
@@ -534,33 +530,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Mateo Cabrera</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bruno Vega</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>Isabella Palacios</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Valentina Fuentes</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
     </row>
@@ -578,12 +574,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Samuel Ortega</t>
+          <t>Lucía Rojas</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -593,20 +589,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Samuel Molina</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Lucía Mendoza</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Gabriel Romero</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Lucy Bennett</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -622,33 +618,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Valentina Fuentes</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sofía Medina</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Bruno Vega</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Nicholas Reed</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Valentina Salazar</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Mateo Cabrera</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
+          <t>Nicolás Mendoza</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
     </row>
@@ -666,7 +662,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Tomás Ortega</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -676,25 +672,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomas Walker</t>
+          <t>Mariana Campos</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lucia Mendoza</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Samuel Ortega</t>
-        </is>
-      </c>
+          <t>Samuel Molina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>Mateo Santos</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -710,12 +706,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nicholas Reed</t>
+          <t>Isabella Palacios</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Matthew Brooks</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -723,16 +719,20 @@
           <t>Bruno Vega</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Mateo Cabrera</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Isabella Palacios</t>
+          <t>Nicolás Mendoza</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Matthew Brooks</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
     </row>
@@ -750,33 +750,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Gabriel Romero</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sofía Medina</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tomás Ortega</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>Samuel Molina</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Mariana Campos</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Gabriel Romero</t>
+          <t>Samuel Ortega</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Lucy Bennett</t>
+          <t>Lucía Rojas</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
     </row>
@@ -794,7 +798,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Matthew Brooks</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -807,11 +811,15 @@
           <t>Bruno Vega</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Mateo Cabrera</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
+          <t>Mateo Santos</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -829,33 +837,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saturday afternoon</t>
+          <t>Saturday morning</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Valentina Fuentes</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mariana Campos</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Lucia Mendoza</t>
-        </is>
-      </c>
+          <t>Nicolás Mendoza</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Valentina Fuentes</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -874,22 +878,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Valentina Salazar</t>
+          <t>Bruno Vega</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thomas Walker</t>
+          <t>Tomás Ortega</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Matthew Brooks</t>
+          <t>Mateo Cabrera</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -900,7 +904,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
     </row>
@@ -918,12 +922,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lucy Bennett</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -931,20 +935,20 @@
           <t>Mariana Campos</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Samuel Molina</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Gabriel Romero</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
+          <t>Lucía Rojas</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
     </row>
@@ -957,38 +961,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saturday morning</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Thomas Walker</t>
+          <t>Samuel Molina</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bruno Vega</t>
+          <t>Tomás Ortega</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Lucía Mendoza</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Samuel Ortega</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nicholas Reed</t>
+          <t>Mateo Santos</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
     </row>
@@ -1001,40 +1009,40 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saturday afternoon</t>
+          <t>Saturday morning</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Nicolás Mendoza</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Valentina Fuentes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mariana Campos</t>
+          <t>Bruno Vega</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lucia Mendoza</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Mateo Cabrera</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>Valentina Fuentes</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1050,17 +1058,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Gabriel Romero</t>
+          <t>Samuel Ortega</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thomas Walker</t>
+          <t>Mariana Campos</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1068,21 +1076,13 @@
           <t>Samuel Molina</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Samuel Ortega</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
+          <t>Sofía Medina</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1098,37 +1098,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Mateo Cabrera</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tomás Ortega</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>Isabella Palacios</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Bruno Vega</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Valentina Salazar</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Nicholas Reed</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1138,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Samuel Ortega</t>
+          <t>Lucía Rojas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1161,18 +1153,22 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Samuel Molina</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Lucía Mendoza</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Gabriel Romero</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Lucy Bennett</t>
+          <t>Mateo Santos</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
     </row>
@@ -1190,29 +1186,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>Valentina Fuentes</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sofía Medina</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Bruno Vega</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Sophia Carter</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Nicholas Reed</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Mateo Cabrera</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Valentina Fuentes</t>
+          <t>Nicolás Mendoza</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
     </row>
@@ -1230,22 +1234,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>Tomás Ortega</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Daniel Herrera</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thomas Walker</t>
+          <t>Mariana Campos</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lucia Mendoza</t>
+          <t>Samuel Molina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1255,14 +1259,10 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
+          <t>Daniel Herrera</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Nicholas Reed</t>
+          <t>Isabella Palacios</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Valentina Salazar</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1293,18 +1293,18 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Matthew Brooks</t>
+          <t>Mateo Cabrera</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Isabella Palacios</t>
+          <t>Mateo Santos</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Valentina Salazar</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
     </row>
@@ -1322,33 +1322,37 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>Gabriel Romero</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Samuel Molina</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Camila Miranda</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mariana Campos</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Tomás Ortega</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lucía Mendoza</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Gabriel Romero</t>
+          <t>Samuel Ortega</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Lucy Bennett</t>
+          <t>Lucía Rojas</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Samuel Molina</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1370,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Matthew Brooks</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1379,16 +1383,20 @@
           <t>Bruno Vega</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Mateo Cabrera</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
+          <t>Nicolás Mendoza</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
     </row>
@@ -1401,40 +1409,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saturday afternoon</t>
+          <t>Saturday morning</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tomás Ortega</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>Valentina Fuentes</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Thomas Walker</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Lucia Mendoza</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Samuel Ortega</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Daniel Herrera</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Camila Miranda</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1450,22 +1454,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Valentina Salazar</t>
+          <t>Bruno Vega</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bruno Vega</t>
+          <t>Nicolás Mendoza</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Matthew Brooks</t>
+          <t>Mateo Cabrera</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1476,7 +1480,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1498,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Lucy Bennett</t>
+          <t>Sofía Medina</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1507,20 +1511,20 @@
           <t>Mariana Campos</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Samuel Molina</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Samuel Ortega</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Matthew Turner</t>
+          <t>Mateo Santos</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
     </row>
@@ -1533,38 +1537,42 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saturday morning</t>
+          <t>Saturday afternoon</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Thomas Walker</t>
+          <t>Samuel Molina</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bruno Vega</t>
+          <t>Tomás Ortega</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Matthew Brooks</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Lucía Mendoza</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Gabriel Romero</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Nicholas Reed</t>
+          <t>Lucía Rojas</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Camila Miranda</t>
+          <t>Daniel Herrera</t>
         </is>
       </c>
     </row>
@@ -1577,30 +1585,34 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saturday afternoon</t>
+          <t>Saturday morning</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sophia Carter</t>
+          <t>Nicolás Mendoza</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mariana Campos</t>
+          <t>Bruno Vega</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lucia Mendoza</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Mateo Cabrera</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>Valentina Fuentes</t>
@@ -1608,7 +1620,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Daniel Herrera</t>
+          <t>Camila Miranda</t>
         </is>
       </c>
     </row>
